--- a/docs/files/rocscience/vp072b.xlsx
+++ b/docs/files/rocscience/vp072b.xlsx
@@ -15075,7 +15075,7 @@
         <v>227.0</v>
       </c>
       <c r="D8" s="3">
-        <v>0.0</v>
+        <v>397.5</v>
       </c>
       <c r="E8" s="3">
         <v>227.0</v>
@@ -15131,10 +15131,10 @@
         <v>227.0</v>
       </c>
       <c r="D9" s="3">
-        <v>397.5</v>
+        <v>440.0</v>
       </c>
       <c r="E9" s="3">
-        <v>227.0</v>
+        <v>312.0</v>
       </c>
       <c r="G9" s="3">
         <v>905.0</v>
@@ -15187,7 +15187,7 @@
         <v>317.0</v>
       </c>
       <c r="D10" s="3">
-        <v>440.0</v>
+        <v>465.0</v>
       </c>
       <c r="E10" s="3">
         <v>312.0</v>
@@ -15235,10 +15235,10 @@
         <v>317.0</v>
       </c>
       <c r="D11" s="3">
-        <v>465.0</v>
+        <v>507.5</v>
       </c>
       <c r="E11" s="3">
-        <v>312.0</v>
+        <v>227.0</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
@@ -15282,12 +15282,8 @@
       <c r="B12" s="3">
         <v>227.0</v>
       </c>
-      <c r="D12" s="3">
-        <v>507.5</v>
-      </c>
-      <c r="E12" s="3">
-        <v>227.0</v>
-      </c>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
       <c r="J12" s="3"/>
@@ -15330,12 +15326,8 @@
       <c r="B13" s="3">
         <v>227.0</v>
       </c>
-      <c r="D13" s="3">
-        <v>905.0</v>
-      </c>
-      <c r="E13" s="3">
-        <v>227.0</v>
-      </c>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
       <c r="J13" s="3"/>
@@ -17475,10 +17467,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="3">
-        <v>700.0</v>
+        <v>695.0</v>
       </c>
       <c r="C3" s="3">
-        <v>320.0</v>
+        <v>390.0</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
@@ -17486,7 +17478,7 @@
         </is>
       </c>
       <c r="E3" s="3">
-        <v>200.0</v>
+        <v>197.0</v>
       </c>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>

--- a/docs/files/rocscience/vp072b.xlsx
+++ b/docs/files/rocscience/vp072b.xlsx
@@ -13432,10 +13432,10 @@
         <v>0.0</v>
       </c>
       <c r="AF10" s="3">
-        <v>0.0</v>
+        <v>100000.0</v>
       </c>
       <c r="AG10" s="3">
-        <v>0.0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.2">
@@ -13541,10 +13541,10 @@
         <v>0.0</v>
       </c>
       <c r="AF11" s="3">
-        <v>0.0</v>
+        <v>100000.0</v>
       </c>
       <c r="AG11" s="3">
-        <v>0.0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.2">
@@ -13650,10 +13650,10 @@
         <v>0.0</v>
       </c>
       <c r="AF12" s="3">
-        <v>0.0</v>
+        <v>100000.0</v>
       </c>
       <c r="AG12" s="3">
-        <v>0.0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="13" spans="1:33" x14ac:dyDescent="0.2">
@@ -13759,10 +13759,10 @@
         <v>0.0</v>
       </c>
       <c r="AF13" s="3">
-        <v>0.0</v>
+        <v>100000.0</v>
       </c>
       <c r="AG13" s="3">
-        <v>0.0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="14" spans="1:33" x14ac:dyDescent="0.2">
